--- a/data/chinese/P3T1_Chapter4.xlsx
+++ b/data/chinese/P3T1_Chapter4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AC76FB-2FCD-E349-AFED-AFF08CF23F92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC5FC1F-3EB9-1842-B67C-8A7547E13155}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,9 +59,6 @@
   <si>
     <t>暫沒有必懂寫生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>詞語</t>
   </si>
   <si>
     <t>解釋</t>
@@ -555,13 +552,13 @@
   <sheetData>
     <row r="1" spans="1:11" ht="27">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -576,13 +573,13 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -591,13 +588,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -606,13 +603,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -621,13 +618,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -636,13 +633,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -651,13 +648,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -666,13 +663,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -681,13 +678,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -697,13 +694,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>

--- a/data/chinese/P3T1_Chapter4.xlsx
+++ b/data/chinese/P3T1_Chapter4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC5FC1F-3EB9-1842-B67C-8A7547E13155}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EECDD1-D367-514F-B6A2-08C7C5220B07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,14 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暫沒有需記認寫生字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暫沒有必懂寫生字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>解釋</t>
   </si>
   <si>
@@ -146,6 +138,90 @@
   </si>
   <si>
     <t>大樹擋住強烈的陽光。</t>
+  </si>
+  <si>
+    <t>被子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>搖頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取暖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓋住</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮住</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讓身體變得溫暖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天冷時，我們靠在火爐旁取暖。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用物品擋在前面，令後面的東西不被看見</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡覺時蓋在身上保暖的物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上睡覺，我蓋好柔軟的被子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>擺動頭部，多表示不同意</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妹妹輕輕搖頭，表示不想吃糖。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把地上的東西撿起來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我彎腰拾起地上的落葉。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偏僻、不太引人注意的地方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小貓躲在房間的角落休息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用東西遮在上面，把底下的東西遮住</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我用布蓋住桌上的書本。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烏雲遮住了天上的太陽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -555,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -573,13 +649,13 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -588,13 +664,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -603,13 +679,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -618,13 +694,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -633,13 +709,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -648,13 +724,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -663,13 +739,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -678,13 +754,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -694,13 +770,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -913,13 +989,13 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="7" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -927,45 +1003,93 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="27">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="27">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="27">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="27">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="27">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="27">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="27">

--- a/data/chinese/P3T1_Chapter4.xlsx
+++ b/data/chinese/P3T1_Chapter4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Github/ChineseLearning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EECDD1-D367-514F-B6A2-08C7C5220B07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478A0909-9654-094F-8E40-32974427CC08}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -221,6 +221,23 @@
   </si>
   <si>
     <t>烏雲遮住了天上的太陽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向晚意不適，
+驅車登古原。
+夕陽無限好，
+只是近黃昏。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《登樂遊原》【唐】李商隱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【解釋】：傍晚時分，我心情不太好， 於是駕著車，登上樂遊原這個古老高地。 
+夕陽的景色真是美極了，可惜美好的時光快要結束，天馬上就要黑了。
+【簡單中心思想】：詩人看見美麗的夕陽，讚嘆景色動人，同時感嘆美好的事物留不住，很快就會消逝。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -228,7 +245,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -276,6 +293,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -308,7 +332,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -332,6 +356,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1278,7 +1308,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1293,11 +1323,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+    <row r="2" spans="1:3" ht="112">
+      <c r="A2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
+      <c r="A3" s="8"/>
       <c r="B3" s="6"/>
     </row>
     <row r="4" spans="1:3">
